--- a/outputs/final_consolation_200_with_journal_replacements_manychat_enriched.xlsx
+++ b/outputs/final_consolation_200_with_journal_replacements_manychat_enriched.xlsx
@@ -14170,7 +14170,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14180,40 +14180,40 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Saiful</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kumar</t>
+          <t>Haizam</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>1558303682</t>
+          <t>537089163</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-04-15T21:57:12+08:00</t>
+          <t>2026-03-17T20:34:37+08:00</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/1558303682</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/537089163</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/p/1BMM3FeM3B/</t>
+          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -14238,7 +14238,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14248,40 +14248,44 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Saiful</t>
+          <t>Salmah</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Haizam</t>
+          <t>Jaafar</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>537089163</t>
+          <t>26750312877989179</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-03-17T20:34:37+08:00</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>2026-04-12T09:43:51+08:00</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-04-12T09:44:00+08:00</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/537089163</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26750312877989179</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -14296,7 +14300,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
+          <t>Saya bantu orang menunjukan jalan.</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -14306,7 +14310,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14316,44 +14320,44 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Salmah</t>
+          <t>Sariffudin</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jaafar</t>
+          <t>Fiza</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>26750312877989179</t>
+          <t>25640455475627828</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-04-12T09:43:51+08:00</t>
+          <t>2026-04-17T16:13:56+08:00</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-04-12T09:44:00+08:00</t>
+          <t>2026-04-17T16:14:04+08:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26750312877989179</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25640455475627828</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -14368,7 +14372,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Saya bantu orang menunjukan jalan.</t>
+          <t>saya sayang family saya</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -14378,7 +14382,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14388,44 +14392,44 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sariffudin</t>
+          <t>Shameel</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fiza</t>
+          <t>Isfahan</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>25640455475627828</t>
+          <t>25409058178770177</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-04-17T16:13:56+08:00</t>
+          <t>2026-04-12T10:26:45+08:00</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-04-17T16:14:04+08:00</t>
+          <t>2026-04-12T10:26:53+08:00</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25640455475627828</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25409058178770177</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -14440,7 +14444,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>saya sayang family saya</t>
+          <t>Saya suka berlari sambil bersedekah</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -14450,7 +14454,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -14460,44 +14464,44 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Shameel</t>
+          <t>Shazlin</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Isfahan</t>
+          <t>Rosly</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>25409058178770177</t>
+          <t>26809398435345201</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-04-12T10:26:45+08:00</t>
+          <t>2026-04-12T08:22:52+08:00</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-04-12T10:26:53+08:00</t>
+          <t>2026-04-12T08:23:01+08:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25409058178770177</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26809398435345201</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -14512,7 +14516,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Saya suka berlari sambil bersedekah</t>
+          <t>Saya Bantu jiran angkat air</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -14522,7 +14526,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -14532,44 +14536,40 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Shazlin</t>
+          <t>Shera</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosly</t>
+          <t>Nazri</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>26809398435345201</t>
+          <t>187412901</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-04-12T08:22:52+08:00</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>2026-04-12T08:23:01+08:00</t>
-        </is>
-      </c>
+          <t>2026-04-03T13:41:35+08:00</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26809398435345201</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/187412901</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Saya Bantu jiran angkat air</t>
+          <t>Saya bantu keluarga saya mengecat rumah</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -58272,7 +58272,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -58282,27 +58282,27 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Saiful</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kumar</t>
+          <t>Haizam</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>1558303682</t>
+          <t>537089163</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -58314,13 +58314,13 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-04-15T21:57:12+08:00</t>
+          <t>2026-03-17T20:34:37+08:00</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/1558303682</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/537089163</t>
         </is>
       </c>
       <c r="N196" t="n">
@@ -58343,51 +58343,51 @@
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>2026-04-15 21:55:40 GMT+8</t>
+          <t>2026-03-16 23:30:39 GMT+8</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2026-04-15 21:57:12 GMT+8</t>
+          <t>2026-03-16 23:34:04 GMT+8</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>2026-04-15 21:55:20 GMT+8</t>
+          <t>2026-03-16 23:24:24 GMT+8</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>2026-04-15 21:54:41 GMT+8</t>
+          <t>2026-02-20 22:23:49 GMT+8</t>
         </is>
       </c>
       <c r="X196" t="n">
-        <v>35766</v>
+        <v>15579</v>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-04-15 21:57:12 GMT+8</t>
+          <t>2026-03-16 23:30:39 GMT+8</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/p/1BMM3FeM3B/</t>
+          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
         </is>
       </c>
       <c r="AA196" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="AD196" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF196" t="n">
         <v>0</v>
@@ -58399,13 +58399,13 @@
         <v>0</v>
       </c>
       <c r="AI196" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL196" t="n">
         <v>0</v>
@@ -58429,7 +58429,7 @@
       <c r="AQ196" t="inlineStr"/>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="AS196" t="n">
@@ -58443,17 +58443,17 @@
       <c r="AU196" t="inlineStr"/>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/ava/594456394024035/1558303682/c701a60bd001586d43c7290a21280bc5</t>
+          <t>https://app.manychat.com/ava/594456394024035/537089163/dcfe9689f587aa1aa82c69d6414ae977</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>zh_CN</t>
+          <t>ms_MY</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Malay</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -58471,17 +58471,17 @@
       <c r="BC196" t="inlineStr"/>
       <c r="BD196" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/p/1BMM3FeM3B/</t>
+          <t>Saya berbuka puasa bersama ahli keluarga dengan hidangan air Tropicana Twister yang sangat sedap.</t>
         </is>
       </c>
       <c r="BE196" t="inlineStr">
         <is>
-          <t>2026-04-15T21:54:41+08:00</t>
+          <t>2026-02-20T22:23:49+08:00</t>
         </is>
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>[{"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}]</t>
+          <t>[{"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12622771, "name": "Journal Count", "type": "text", "description": "", "value": "2"}, {"id": 12617108, "name": "Orange Count", "type": "number", "description": "", "value": 25}, {"id": 12622772, "name": "Pledge Count", "type": "text", "description": "", "value": "1"}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": true}]</t>
         </is>
       </c>
       <c r="BG196" t="inlineStr">
@@ -58493,7 +58493,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -58503,27 +58503,27 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Saiful</t>
+          <t>Salmah</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Haizam</t>
+          <t>Jaafar</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>537089163</t>
+          <t>26750312877989179</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -58535,13 +58535,17 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-03-17T20:34:37+08:00</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
+          <t>2026-04-12T09:43:51+08:00</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-04-12T09:44:00+08:00</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/537089163</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26750312877989179</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -58564,48 +58568,48 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:39 GMT+8</t>
+          <t>2026-04-12 09:42:11 GMT+8</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2026-03-16 23:34:04 GMT+8</t>
+          <t>2026-04-12 09:43:52 GMT+8</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>2026-03-16 23:24:24 GMT+8</t>
+          <t>2026-04-12 09:40:28 GMT+8</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>2026-02-20 22:23:49 GMT+8</t>
+          <t>2026-04-12 09:40:28 GMT+8</t>
         </is>
       </c>
       <c r="X197" t="n">
-        <v>15579</v>
+        <v>33096</v>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:39 GMT+8</t>
+          <t>2026-04-12 09:43:52 GMT+8</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
+          <t>Saya bantu orang menunjukan jalan.</t>
         </is>
       </c>
       <c r="AA197" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="AB197" t="n">
-        <v>-2.4</v>
+        <v>10.85</v>
       </c>
       <c r="AC197" t="n">
-        <v>2.6</v>
+        <v>0.85</v>
       </c>
       <c r="AD197" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE197" t="n">
         <v>5</v>
@@ -58620,10 +58624,10 @@
         <v>0</v>
       </c>
       <c r="AI197" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK197" t="n">
         <v>1</v>
@@ -58650,7 +58654,7 @@
       <c r="AQ197" t="inlineStr"/>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="AS197" t="n">
@@ -58664,17 +58668,17 @@
       <c r="AU197" t="inlineStr"/>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/ava/594456394024035/537089163/dcfe9689f587aa1aa82c69d6414ae977</t>
+          <t>https://app.manychat.com/ava/594456394024035/26750312877989179/2d21ee6051339a7b299de4e909b73a57</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>ms_MY</t>
+          <t>en_GB</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Malay</t>
+          <t>English</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -58692,17 +58696,17 @@
       <c r="BC197" t="inlineStr"/>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>Saya berbuka puasa bersama ahli keluarga dengan hidangan air Tropicana Twister yang sangat sedap.</t>
+          <t>Saya bantu orang menunjukan jalan.</t>
         </is>
       </c>
       <c r="BE197" t="inlineStr">
         <is>
-          <t>2026-02-20T22:23:49+08:00</t>
+          <t>2026-04-12T09:40:28+08:00</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>[{"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12622771, "name": "Journal Count", "type": "text", "description": "", "value": "2"}, {"id": 12617108, "name": "Orange Count", "type": "number", "description": "", "value": 25}, {"id": 12622772, "name": "Pledge Count", "type": "text", "description": "", "value": "1"}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": true}]</t>
+          <t>[{"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": false}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}]</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr">
@@ -58714,7 +58718,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -58724,27 +58728,27 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Salmah</t>
+          <t>Sariffudin</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jaafar</t>
+          <t>Fiza</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>26750312877989179</t>
+          <t>25640455475627828</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -58756,17 +58760,17 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-04-12T09:43:51+08:00</t>
+          <t>2026-04-17T16:13:56+08:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-04-12T09:44:00+08:00</t>
+          <t>2026-04-17T16:14:04+08:00</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26750312877989179</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25640455475627828</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -58789,48 +58793,48 @@
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>2026-04-12 09:42:11 GMT+8</t>
+          <t>2026-04-17 15:40:28 GMT+8</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2026-04-12 09:43:52 GMT+8</t>
+          <t>2026-04-17 16:13:56 GMT+8</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>2026-04-12 09:40:28 GMT+8</t>
+          <t>2026-04-17 16:12:47 GMT+8</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>2026-04-12 09:40:28 GMT+8</t>
+          <t>2026-04-17 15:39:37 GMT+8</t>
         </is>
       </c>
       <c r="X198" t="n">
-        <v>33096</v>
+        <v>36502</v>
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-04-12 09:43:52 GMT+8</t>
+          <t>2026-04-17 15:40:28 GMT+8</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>Saya bantu orang menunjukan jalan.</t>
+          <t>saya sayang family saya</t>
         </is>
       </c>
       <c r="AA198" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AB198" t="n">
-        <v>10.85</v>
+        <v>-9.43</v>
       </c>
       <c r="AC198" t="n">
-        <v>0.85</v>
+        <v>0.575</v>
       </c>
       <c r="AD198" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE198" t="n">
         <v>5</v>
@@ -58842,13 +58846,13 @@
         <v>0</v>
       </c>
       <c r="AH198" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI198" t="n">
         <v>0</v>
       </c>
       <c r="AJ198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK198" t="n">
         <v>1</v>
@@ -58860,7 +58864,7 @@
         <v>0</v>
       </c>
       <c r="AN198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -58875,7 +58879,7 @@
       <c r="AQ198" t="inlineStr"/>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="AS198" t="n">
@@ -58889,17 +58893,17 @@
       <c r="AU198" t="inlineStr"/>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/ava/594456394024035/26750312877989179/2d21ee6051339a7b299de4e909b73a57</t>
+          <t>https://app.manychat.com/ava/594456394024035/25640455475627828/efb9573695afb11134fa02c545ef0e47</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>en_GB</t>
+          <t>ms_MY</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Malay</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -58917,17 +58921,17 @@
       <c r="BC198" t="inlineStr"/>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>Saya bantu orang menunjukan jalan.</t>
+          <t>saya suka bercuti bersama keluarga</t>
         </is>
       </c>
       <c r="BE198" t="inlineStr">
         <is>
-          <t>2026-04-12T09:40:28+08:00</t>
+          <t>2026-04-17T15:39:37+08:00</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>[{"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": false}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}]</t>
+          <t>[{"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": false}]</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr">
@@ -58939,7 +58943,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -58949,27 +58953,27 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sariffudin</t>
+          <t>Shameel</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fiza</t>
+          <t>Isfahan</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>25640455475627828</t>
+          <t>25409058178770177</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -58981,17 +58985,17 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-04-17T16:13:56+08:00</t>
+          <t>2026-04-12T10:26:45+08:00</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-04-17T16:14:04+08:00</t>
+          <t>2026-04-12T10:26:53+08:00</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25640455475627828</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25409058178770177</t>
         </is>
       </c>
       <c r="N199" t="n">
@@ -59014,51 +59018,51 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>2026-04-17 15:40:28 GMT+8</t>
+          <t>2026-04-12 09:57:57 GMT+8</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2026-04-17 16:13:56 GMT+8</t>
+          <t>2026-04-12 10:26:46 GMT+8</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>2026-04-17 16:12:47 GMT+8</t>
+          <t>2026-04-12 09:56:09 GMT+8</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>2026-04-17 15:39:37 GMT+8</t>
+          <t>2026-04-12 09:56:08 GMT+8</t>
         </is>
       </c>
       <c r="X199" t="n">
-        <v>36502</v>
+        <v>33118</v>
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-04-17 15:40:28 GMT+8</t>
+          <t>2026-04-12 09:57:57 GMT+8</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>saya sayang family saya</t>
+          <t>Saya suka berlari sambil bersedekah</t>
         </is>
       </c>
       <c r="AA199" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="AB199" t="n">
-        <v>-9.43</v>
+        <v>5.88</v>
       </c>
       <c r="AC199" t="n">
-        <v>0.575</v>
+        <v>0.875</v>
       </c>
       <c r="AD199" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE199" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF199" t="n">
         <v>0</v>
@@ -59067,26 +59071,26 @@
         <v>0</v>
       </c>
       <c r="AH199" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI199" t="n">
         <v>0</v>
       </c>
       <c r="AJ199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN199" t="n">
         <v>1</v>
       </c>
-      <c r="AL199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>2</v>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>selected_highest_heuristic_score</t>
@@ -59104,7 +59108,7 @@
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="AS199" t="n">
@@ -59118,17 +59122,17 @@
       <c r="AU199" t="inlineStr"/>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/ava/594456394024035/25640455475627828/efb9573695afb11134fa02c545ef0e47</t>
+          <t>https://app.manychat.com/ava/594456394024035/25409058178770177/0a35e34c3e1cf4782981564798cb078f</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>ms_MY</t>
+          <t>en_GB</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Malay</t>
+          <t>English</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -59146,17 +59150,17 @@
       <c r="BC199" t="inlineStr"/>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>saya suka bercuti bersama keluarga</t>
+          <t>Saya suka berlari dan berlari</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>2026-04-17T15:39:37+08:00</t>
+          <t>2026-04-12T09:56:08+08:00</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>[{"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": false}]</t>
+          <t>[{"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": false}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12617108, "name": "Orange Count", "type": "number", "description": "", "value": 15}, {"id": 12622771, "name": "Journal Count", "type": "text", "description": "", "value": "1"}, {"id": 12622772, "name": "Pledge Count", "type": "text", "description": "", "value": "1"}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}]</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr">
@@ -59168,7 +59172,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -59178,27 +59182,27 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Shameel</t>
+          <t>Shazlin</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Isfahan</t>
+          <t>Rosly</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>25409058178770177</t>
+          <t>26809398435345201</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -59210,17 +59214,17 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-04-12T10:26:45+08:00</t>
+          <t>2026-04-12T08:22:52+08:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-04-12T10:26:53+08:00</t>
+          <t>2026-04-12T08:23:01+08:00</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25409058178770177</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26809398435345201</t>
         </is>
       </c>
       <c r="N200" t="n">
@@ -59243,52 +59247,52 @@
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:57:57 GMT+8</t>
+          <t>2026-04-12 08:22:19 GMT+8</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2026-04-12 10:26:46 GMT+8</t>
+          <t>2026-04-12 08:22:53 GMT+8</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:56:09 GMT+8</t>
+          <t>2026-04-12 08:20:50 GMT+8</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:56:08 GMT+8</t>
+          <t>2026-04-12 08:20:49 GMT+8</t>
         </is>
       </c>
       <c r="X200" t="n">
-        <v>33118</v>
+        <v>32871</v>
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:57:57 GMT+8</t>
+          <t>2026-04-12 08:22:53 GMT+8</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>Saya suka berlari sambil bersedekah</t>
+          <t>Saya Bantu jiran angkat air</t>
         </is>
       </c>
       <c r="AA200" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AB200" t="n">
-        <v>5.88</v>
+        <v>15.68</v>
       </c>
       <c r="AC200" t="n">
-        <v>0.875</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="AD200" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE200" t="n">
         <v>5</v>
       </c>
-      <c r="AE200" t="n">
-        <v>0</v>
-      </c>
       <c r="AF200" t="n">
         <v>0</v>
       </c>
@@ -59302,10 +59306,10 @@
         <v>0</v>
       </c>
       <c r="AJ200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK200" t="n">
         <v>1</v>
-      </c>
-      <c r="AK200" t="n">
-        <v>0</v>
       </c>
       <c r="AL200" t="n">
         <v>0</v>
@@ -59333,7 +59337,7 @@
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>Shameel Isfahan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="AS200" t="n">
@@ -59347,17 +59351,17 @@
       <c r="AU200" t="inlineStr"/>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/ava/594456394024035/25409058178770177/0a35e34c3e1cf4782981564798cb078f</t>
+          <t>https://app.manychat.com/ava/594456394024035/26809398435345201/933c5d823826bfae3a4e0de8cdfdbf01</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>en_GB</t>
+          <t>ms_MY</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Malay</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -59375,17 +59379,17 @@
       <c r="BC200" t="inlineStr"/>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>Saya suka berlari dan berlari</t>
+          <t>Saya Bantu jiran angkat air</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>2026-04-12T09:56:08+08:00</t>
+          <t>2026-04-12T08:20:49+08:00</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>[{"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": false}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12617108, "name": "Orange Count", "type": "number", "description": "", "value": 15}, {"id": 12622771, "name": "Journal Count", "type": "text", "description": "", "value": "1"}, {"id": 12622772, "name": "Pledge Count", "type": "text", "description": "", "value": "1"}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}]</t>
+          <t>[{"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}]</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr">
@@ -59397,7 +59401,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -59407,27 +59411,27 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Shazlin</t>
+          <t>Shera</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosly</t>
+          <t>Nazri</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>26809398435345201</t>
+          <t>187412901</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -59439,17 +59443,13 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-04-12T08:22:52+08:00</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>2026-04-12T08:23:01+08:00</t>
-        </is>
-      </c>
+          <t>2026-04-03T13:41:35+08:00</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26809398435345201</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/187412901</t>
         </is>
       </c>
       <c r="N201" t="n">
@@ -59472,45 +59472,45 @@
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2026-04-12 08:22:19 GMT+8</t>
+          <t>2026-03-16 05:58:14 GMT+8</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2026-04-12 08:22:53 GMT+8</t>
+          <t>2026-03-16 05:58:47 GMT+8</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>2026-04-12 08:20:50 GMT+8</t>
+          <t>2026-04-03 13:41:35 GMT+8</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>2026-04-12 08:20:49 GMT+8</t>
+          <t>2026-03-16 05:56:01 GMT+8</t>
         </is>
       </c>
       <c r="X201" t="n">
-        <v>32871</v>
+        <v>14177</v>
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-04-12 08:22:53 GMT+8</t>
+          <t>2026-03-16 05:58:47 GMT+8</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>Saya Bantu jiran angkat air</t>
+          <t>Saya bantu keluarga saya mengecat rumah</t>
         </is>
       </c>
       <c r="AA201" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AB201" t="n">
-        <v>15.68</v>
+        <v>15.98</v>
       </c>
       <c r="AC201" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="AD201" t="n">
         <v>10</v>
@@ -59562,7 +59562,7 @@
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>Shazlin Rosly</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="AS201" t="n">
@@ -59576,7 +59576,7 @@
       <c r="AU201" t="inlineStr"/>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/ava/594456394024035/26809398435345201/933c5d823826bfae3a4e0de8cdfdbf01</t>
+          <t>https://app.manychat.com/ava/594456394024035/187412901/b00fd5778438bd26a177cbcca7f9fe3a</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
@@ -59604,17 +59604,17 @@
       <c r="BC201" t="inlineStr"/>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>Saya Bantu jiran angkat air</t>
+          <t>Saya bantu keluarga saya mengecat rumah</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>2026-04-12T08:20:49+08:00</t>
+          <t>2026-03-16T05:56:01+08:00</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>[{"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}]</t>
+          <t>[{"id": 12617114, "name": "Added Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12617111, "name": "Joined Contest", "type": "boolean", "description": "", "value": true}, {"id": 12617109, "name": "Pledge Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617112, "name": "Journal Allowed", "type": "boolean", "description": "", "value": true}, {"id": 12617113, "name": "Has Pledge", "type": "boolean", "description": "", "value": true}, {"id": 12622769, "name": "Submit Journal Check", "type": "boolean", "description": "", "value": true}, {"id": 12622770, "name": "Submit Journal Error Message", "type": "text", "description": "", "value": "Journal submitted successfully"}, {"id": 12622771, "name": "Journal Count", "type": "text", "description": "", "value": "2"}, {"id": 12622772, "name": "Pledge Count", "type": "text", "description": "", "value": "1"}, {"id": 12617108, "name": "Orange Count", "type": "number", "description": "", "value": 25}]</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr">
